--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/201.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/201.xlsx
@@ -426,13 +426,13 @@
         <v>-1.720793133622628</v>
       </c>
       <c r="E2">
-        <v>-16.42845895189622</v>
+        <v>-16.6453547429676</v>
       </c>
       <c r="F2">
-        <v>-3.27918114654145</v>
+        <v>-3.039118616475348</v>
       </c>
       <c r="G2">
-        <v>-10.50966233018418</v>
+        <v>-11.20694929493872</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.825301545581321</v>
       </c>
       <c r="E3">
-        <v>-18.21271393871041</v>
+        <v>-18.22911154309218</v>
       </c>
       <c r="F3">
-        <v>-3.463221189156222</v>
+        <v>-3.316678025396573</v>
       </c>
       <c r="G3">
-        <v>-8.861874704012882</v>
+        <v>-11.64902961461637</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.837456545094537</v>
       </c>
       <c r="E4">
-        <v>-18.16260184534153</v>
+        <v>-18.41433971542792</v>
       </c>
       <c r="F4">
-        <v>-3.024376990175128</v>
+        <v>-2.994353642028063</v>
       </c>
       <c r="G4">
-        <v>-9.895311152279472</v>
+        <v>-11.03528426654535</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.730675711933733</v>
       </c>
       <c r="E5">
-        <v>-17.10350045832361</v>
+        <v>-18.88525119901156</v>
       </c>
       <c r="F5">
-        <v>-2.820799073997927</v>
+        <v>-2.634247421417867</v>
       </c>
       <c r="G5">
-        <v>-10.64993345522864</v>
+        <v>-10.79143279266817</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.507985654624869</v>
       </c>
       <c r="E6">
-        <v>-18.12388339257594</v>
+        <v>-19.64392003493859</v>
       </c>
       <c r="F6">
-        <v>-2.869753930768572</v>
+        <v>-2.839443139132736</v>
       </c>
       <c r="G6">
-        <v>-9.809524985720339</v>
+        <v>-10.99474994696251</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.171638901347603</v>
       </c>
       <c r="E7">
-        <v>-19.35946846862079</v>
+        <v>-20.37497876484086</v>
       </c>
       <c r="F7">
-        <v>-2.367909077334965</v>
+        <v>-3.088987990858684</v>
       </c>
       <c r="G7">
-        <v>-8.080420429467919</v>
+        <v>-10.71150629171355</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.7309204452967978</v>
       </c>
       <c r="E8">
-        <v>-20.98259582176805</v>
+        <v>-21.44620287677731</v>
       </c>
       <c r="F8">
-        <v>-3.220361262370866</v>
+        <v>-2.557565450940717</v>
       </c>
       <c r="G8">
-        <v>-8.640044979062937</v>
+        <v>-9.916872735376746</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.2055913611740861</v>
       </c>
       <c r="E9">
-        <v>-23.4110035938033</v>
+        <v>-22.03922013350377</v>
       </c>
       <c r="F9">
-        <v>-3.803052289215497</v>
+        <v>-2.653916177029938</v>
       </c>
       <c r="G9">
-        <v>-6.679546531797619</v>
+        <v>-9.292861385588441</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.3889612725972398</v>
       </c>
       <c r="E10">
-        <v>-22.01122057871434</v>
+        <v>-23.53261576327929</v>
       </c>
       <c r="F10">
-        <v>-2.972298359928526</v>
+        <v>-2.977976818474716</v>
       </c>
       <c r="G10">
-        <v>-7.178243801287891</v>
+        <v>-9.207386410309999</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.028988166722136</v>
       </c>
       <c r="E11">
-        <v>-21.51045739447214</v>
+        <v>-23.46327576927384</v>
       </c>
       <c r="F11">
-        <v>-3.572038844657576</v>
+        <v>-2.872128860112398</v>
       </c>
       <c r="G11">
-        <v>-6.112135579094234</v>
+        <v>-8.271263448170284</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.687180334680729</v>
       </c>
       <c r="E12">
-        <v>-23.20986236380461</v>
+        <v>-23.41934051445142</v>
       </c>
       <c r="F12">
-        <v>-3.42121799162987</v>
+        <v>-2.991372347745387</v>
       </c>
       <c r="G12">
-        <v>-6.965868994398106</v>
+        <v>-7.79637562219845</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.343395595788847</v>
       </c>
       <c r="E13">
-        <v>-22.59490465051099</v>
+        <v>-24.17108531362073</v>
       </c>
       <c r="F13">
-        <v>-3.639390913076996</v>
+        <v>-2.66290893355473</v>
       </c>
       <c r="G13">
-        <v>-6.183120296547287</v>
+        <v>-7.1594034866239</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.970172613600119</v>
       </c>
       <c r="E14">
-        <v>-26.16666154000285</v>
+        <v>-25.05424190001863</v>
       </c>
       <c r="F14">
-        <v>-3.276525400648075</v>
+        <v>-2.408983675002778</v>
       </c>
       <c r="G14">
-        <v>-4.961340291460481</v>
+        <v>-6.828474733427273</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.550953154574538</v>
       </c>
       <c r="E15">
-        <v>-26.72796589325359</v>
+        <v>-25.83641351604548</v>
       </c>
       <c r="F15">
-        <v>-2.772282423583363</v>
+        <v>-2.682558636716537</v>
       </c>
       <c r="G15">
-        <v>-5.834013337794523</v>
+        <v>-6.107557094613422</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.075243623930051</v>
       </c>
       <c r="E16">
-        <v>-25.93542407174918</v>
+        <v>-26.58888739953002</v>
       </c>
       <c r="F16">
-        <v>-3.526895306307212</v>
+        <v>-2.746608004300995</v>
       </c>
       <c r="G16">
-        <v>-5.070512151709027</v>
+        <v>-6.080821128838268</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.531707881884679</v>
       </c>
       <c r="E17">
-        <v>-28.1430642074365</v>
+        <v>-28.15004711435632</v>
       </c>
       <c r="F17">
-        <v>-2.97880352914271</v>
+        <v>-2.304746062871502</v>
       </c>
       <c r="G17">
-        <v>-3.086995481309156</v>
+        <v>-6.215474258102584</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.922365004831634</v>
       </c>
       <c r="E18">
-        <v>-27.91285923125657</v>
+        <v>-28.63730186063364</v>
       </c>
       <c r="F18">
-        <v>-1.725892862204041</v>
+        <v>-2.088411288691189</v>
       </c>
       <c r="G18">
-        <v>-2.72154104868347</v>
+        <v>-5.635556064351833</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.245359850483791</v>
       </c>
       <c r="E19">
-        <v>-29.67440165668528</v>
+        <v>-29.35355700900483</v>
       </c>
       <c r="F19">
-        <v>-2.545872216682799</v>
+        <v>-2.282680011995729</v>
       </c>
       <c r="G19">
-        <v>-3.426819670369804</v>
+        <v>-4.410495308635609</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.498220729301226</v>
       </c>
       <c r="E20">
-        <v>-29.85399414311848</v>
+        <v>-29.34281546865864</v>
       </c>
       <c r="F20">
-        <v>-2.60952893811833</v>
+        <v>-2.083452681418031</v>
       </c>
       <c r="G20">
-        <v>-3.531482567593862</v>
+        <v>-5.089551099105375</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.678406217648277</v>
       </c>
       <c r="E21">
-        <v>-30.43066360867725</v>
+        <v>-29.95031704949863</v>
       </c>
       <c r="F21">
-        <v>-2.437004030769874</v>
+        <v>-1.588248849452667</v>
       </c>
       <c r="G21">
-        <v>-4.447010625933769</v>
+        <v>-4.613825705112106</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.777214045096101</v>
       </c>
       <c r="E22">
-        <v>-29.18412868248186</v>
+        <v>-31.16202801057504</v>
       </c>
       <c r="F22">
-        <v>-2.074006807923908</v>
+        <v>-1.853766281439395</v>
       </c>
       <c r="G22">
-        <v>-1.461676527712888</v>
+        <v>-4.528248102921945</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.783392736043692</v>
       </c>
       <c r="E23">
-        <v>-29.84819769638866</v>
+        <v>-30.5896900304046</v>
       </c>
       <c r="F23">
-        <v>-1.858908786275975</v>
+        <v>-1.710803321594645</v>
       </c>
       <c r="G23">
-        <v>-1.636198556906647</v>
+        <v>-4.219655600478782</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.684878833614414</v>
       </c>
       <c r="E24">
-        <v>-30.34015073444893</v>
+        <v>-31.70229080934914</v>
       </c>
       <c r="F24">
-        <v>-3.065503774989318</v>
+        <v>-1.378669411442184</v>
       </c>
       <c r="G24">
-        <v>-3.380475343365546</v>
+        <v>-4.392949417277471</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.472310731780761</v>
       </c>
       <c r="E25">
-        <v>-30.23661170473756</v>
+        <v>-32.05361435133821</v>
       </c>
       <c r="F25">
-        <v>-2.24465463473762</v>
+        <v>-1.474963808548015</v>
       </c>
       <c r="G25">
-        <v>-2.051284688257086</v>
+        <v>-4.44836794960487</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.13568587322822</v>
       </c>
       <c r="E26">
-        <v>-31.78447808411434</v>
+        <v>-32.06139426968339</v>
       </c>
       <c r="F26">
-        <v>-2.974776006830299</v>
+        <v>-1.271711440760114</v>
       </c>
       <c r="G26">
-        <v>-2.144655314646691</v>
+        <v>-5.008595018488037</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.675381044468071</v>
       </c>
       <c r="E27">
-        <v>-29.98864152502555</v>
+        <v>-31.2213442273645</v>
       </c>
       <c r="F27">
-        <v>-2.215134933971457</v>
+        <v>-1.559149130959723</v>
       </c>
       <c r="G27">
-        <v>-2.109133161010311</v>
+        <v>-4.381402234436493</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.097267937197629</v>
       </c>
       <c r="E28">
-        <v>-30.51226218182146</v>
+        <v>-30.65552724976512</v>
       </c>
       <c r="F28">
-        <v>-2.469782528898651</v>
+        <v>-1.654702967607452</v>
       </c>
       <c r="G28">
-        <v>-2.26571203338122</v>
+        <v>-4.823469311931992</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.409605958240506</v>
       </c>
       <c r="E29">
-        <v>-28.2319762661031</v>
+        <v>-31.55596222873928</v>
       </c>
       <c r="F29">
-        <v>-2.044863185958616</v>
+        <v>-1.314630812633962</v>
       </c>
       <c r="G29">
-        <v>-3.564078198973526</v>
+        <v>-4.645335477554888</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.639446645432012</v>
       </c>
       <c r="E30">
-        <v>-29.73465979606835</v>
+        <v>-30.46390940060456</v>
       </c>
       <c r="F30">
-        <v>-3.047828071348382</v>
+        <v>-1.671744141817843</v>
       </c>
       <c r="G30">
-        <v>-1.841945651626812</v>
+        <v>-5.045136820150513</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.810819399997908</v>
       </c>
       <c r="E31">
-        <v>-29.05266255356518</v>
+        <v>-29.69783424543797</v>
       </c>
       <c r="F31">
-        <v>-2.707185171234364</v>
+        <v>-1.842643792322006</v>
       </c>
       <c r="G31">
-        <v>-2.666036442172049</v>
+        <v>-5.182160300020947</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.9540992879312443</v>
       </c>
       <c r="E32">
-        <v>-30.02152730326925</v>
+        <v>-30.03175939028958</v>
       </c>
       <c r="F32">
-        <v>-2.759061679834683</v>
+        <v>-1.495494066258998</v>
       </c>
       <c r="G32">
-        <v>-3.409353232104609</v>
+        <v>-5.659375439506888</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.1061303513071978</v>
       </c>
       <c r="E33">
-        <v>-28.20508618744555</v>
+        <v>-29.22102668869636</v>
       </c>
       <c r="F33">
-        <v>-2.190485205166353</v>
+        <v>-1.952083551742863</v>
       </c>
       <c r="G33">
-        <v>-5.397309344072642</v>
+        <v>-5.974473163934721</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.7097054413419783</v>
       </c>
       <c r="E34">
-        <v>-28.83173642062697</v>
+        <v>-29.90302619543653</v>
       </c>
       <c r="F34">
-        <v>-2.569131116618604</v>
+        <v>-1.842788756617496</v>
       </c>
       <c r="G34">
-        <v>-5.130797185979155</v>
+        <v>-5.94676720831656</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.462934318878409</v>
       </c>
       <c r="E35">
-        <v>-26.72677943306358</v>
+        <v>-29.16639064979381</v>
       </c>
       <c r="F35">
-        <v>-2.004973153676806</v>
+        <v>-1.701866894053244</v>
       </c>
       <c r="G35">
-        <v>-4.518875948500269</v>
+        <v>-6.492964185204295</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.13181145595331</v>
       </c>
       <c r="E36">
-        <v>-25.90358437100125</v>
+        <v>-28.51362470701015</v>
       </c>
       <c r="F36">
-        <v>-2.011636541064925</v>
+        <v>-1.449867589712801</v>
       </c>
       <c r="G36">
-        <v>-4.336097418731567</v>
+        <v>-6.028524440954401</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.706655002774271</v>
       </c>
       <c r="E37">
-        <v>-27.1596019217687</v>
+        <v>-28.70212696605344</v>
       </c>
       <c r="F37">
-        <v>-2.001860148977086</v>
+        <v>-1.604556090144178</v>
       </c>
       <c r="G37">
-        <v>-6.043574180975928</v>
+        <v>-6.38410682678198</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.173488999657573</v>
       </c>
       <c r="E38">
-        <v>-24.68996239389361</v>
+        <v>-27.21184239792118</v>
       </c>
       <c r="F38">
-        <v>-2.053047455898275</v>
+        <v>-1.186345694799417</v>
       </c>
       <c r="G38">
-        <v>-3.946694499674794</v>
+        <v>-6.989959834287382</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.535316623071174</v>
       </c>
       <c r="E39">
-        <v>-24.88976772406004</v>
+        <v>-26.4693809704676</v>
       </c>
       <c r="F39">
-        <v>-1.828643554847292</v>
+        <v>-1.159036078263923</v>
       </c>
       <c r="G39">
-        <v>-4.584348607630435</v>
+        <v>-6.885085062148811</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.798625872132388</v>
       </c>
       <c r="E40">
-        <v>-24.44510327582487</v>
+        <v>-25.77803242913859</v>
       </c>
       <c r="F40">
-        <v>-1.966717490280719</v>
+        <v>-1.437958979930156</v>
       </c>
       <c r="G40">
-        <v>-6.172983406106039</v>
+        <v>-6.969593358129786</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.971658143273538</v>
       </c>
       <c r="E41">
-        <v>-24.40495835374687</v>
+        <v>-24.76610415585858</v>
       </c>
       <c r="F41">
-        <v>-1.154805605937826</v>
+        <v>-1.283229889496041</v>
       </c>
       <c r="G41">
-        <v>-5.745429760254704</v>
+        <v>-7.720365496616784</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.074639531486636</v>
       </c>
       <c r="E42">
-        <v>-24.14063585439316</v>
+        <v>-23.5321493304565</v>
       </c>
       <c r="F42">
-        <v>-1.348573166963672</v>
+        <v>-0.8978584631004611</v>
       </c>
       <c r="G42">
-        <v>-6.820661845954593</v>
+        <v>-7.807472570846087</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.123571208403623</v>
       </c>
       <c r="E43">
-        <v>-23.39249119205995</v>
+        <v>-23.50985112444273</v>
       </c>
       <c r="F43">
-        <v>-1.207264456822313</v>
+        <v>-1.154755903893658</v>
       </c>
       <c r="G43">
-        <v>-6.208925999025906</v>
+        <v>-8.04043897099014</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.135207805755739</v>
       </c>
       <c r="E44">
-        <v>-20.96269770697835</v>
+        <v>-23.64284334909999</v>
       </c>
       <c r="F44">
-        <v>-1.213295799882096</v>
+        <v>-0.6455253266966897</v>
       </c>
       <c r="G44">
-        <v>-8.514608408579953</v>
+        <v>-8.465317696045744</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.127124197105982</v>
       </c>
       <c r="E45">
-        <v>-22.75065245705679</v>
+        <v>-22.06272744207758</v>
       </c>
       <c r="F45">
-        <v>-1.062571037473115</v>
+        <v>-0.860480040783939</v>
       </c>
       <c r="G45">
-        <v>-8.258759517668457</v>
+        <v>-8.328906667100075</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.109781352143647</v>
       </c>
       <c r="E46">
-        <v>-20.65222552901247</v>
+        <v>-21.83740416087793</v>
       </c>
       <c r="F46">
-        <v>-1.490196656718095</v>
+        <v>-0.7509160262526624</v>
       </c>
       <c r="G46">
-        <v>-9.598282385404984</v>
+        <v>-8.650939984432679</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.092451121403126</v>
       </c>
       <c r="E47">
-        <v>-20.10606892131738</v>
+        <v>-21.4126015996404</v>
       </c>
       <c r="F47">
-        <v>-0.7409706472146516</v>
+        <v>-1.130419297966811</v>
       </c>
       <c r="G47">
-        <v>-9.548389153582626</v>
+        <v>-9.230093442163859</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.081443050877801</v>
       </c>
       <c r="E48">
-        <v>-17.12415029979859</v>
+        <v>-20.58732796800854</v>
       </c>
       <c r="F48">
-        <v>-1.195504124804768</v>
+        <v>-0.9242253975315694</v>
       </c>
       <c r="G48">
-        <v>-9.022264014299493</v>
+        <v>-9.374426606585004</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.076961349759988</v>
       </c>
       <c r="E49">
-        <v>-18.85336621352355</v>
+        <v>-20.27205107912053</v>
       </c>
       <c r="F49">
-        <v>-0.9452949224217748</v>
+        <v>-0.7688882854238005</v>
       </c>
       <c r="G49">
-        <v>-8.612825673639049</v>
+        <v>-9.445818521139387</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.07850051413971</v>
       </c>
       <c r="E50">
-        <v>-18.80966643934953</v>
+        <v>-19.42785295461062</v>
       </c>
       <c r="F50">
-        <v>-1.17786321259475</v>
+        <v>-0.4751160696949838</v>
       </c>
       <c r="G50">
-        <v>-8.946419415994789</v>
+        <v>-8.955725359505681</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.084275691772597</v>
       </c>
       <c r="E51">
-        <v>-17.86734986851543</v>
+        <v>-18.69419940910195</v>
       </c>
       <c r="F51">
-        <v>-0.5019013296645058</v>
+        <v>-0.5188762344826733</v>
       </c>
       <c r="G51">
-        <v>-9.227166919907143</v>
+        <v>-9.625971788295447</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.08837562222505</v>
       </c>
       <c r="E52">
-        <v>-17.91035225769226</v>
+        <v>-18.50541638467019</v>
       </c>
       <c r="F52">
-        <v>-0.4855824918293555</v>
+        <v>-0.8132324492304636</v>
       </c>
       <c r="G52">
-        <v>-9.415854773463444</v>
+        <v>-10.12418571813699</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.086579807687515</v>
       </c>
       <c r="E53">
-        <v>-17.04390574038267</v>
+        <v>-17.71446858601648</v>
       </c>
       <c r="F53">
-        <v>-0.9101862267889234</v>
+        <v>-0.5219693583647266</v>
       </c>
       <c r="G53">
-        <v>-9.283403156982743</v>
+        <v>-10.66781371168625</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.075139763107276</v>
       </c>
       <c r="E54">
-        <v>-15.89051246757705</v>
+        <v>-17.67283832446396</v>
       </c>
       <c r="F54">
-        <v>-0.9836499899061975</v>
+        <v>-0.7835396196771153</v>
       </c>
       <c r="G54">
-        <v>-9.524453909333696</v>
+        <v>-10.49179531590874</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.04973457771871</v>
       </c>
       <c r="E55">
-        <v>-15.65553900826705</v>
+        <v>-17.24263782220929</v>
       </c>
       <c r="F55">
-        <v>-0.1032718829871193</v>
+        <v>-0.4529713239159446</v>
       </c>
       <c r="G55">
-        <v>-10.53262758459011</v>
+        <v>-10.0125574330983</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.010133442303993</v>
       </c>
       <c r="E56">
-        <v>-15.6637174323249</v>
+        <v>-17.59980762414226</v>
       </c>
       <c r="F56">
-        <v>-0.6677197745198968</v>
+        <v>-0.6535522068298169</v>
       </c>
       <c r="G56">
-        <v>-10.20987587887548</v>
+        <v>-10.60229139437299</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.955319086793453</v>
       </c>
       <c r="E57">
-        <v>-13.82128966840818</v>
+        <v>-15.48018743774204</v>
       </c>
       <c r="F57">
-        <v>-1.202358865062934</v>
+        <v>-0.3112459449709772</v>
       </c>
       <c r="G57">
-        <v>-10.41043865928115</v>
+        <v>-11.15787045731902</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.885733179871318</v>
       </c>
       <c r="E58">
-        <v>-12.30062809663248</v>
+        <v>-16.24082615986241</v>
       </c>
       <c r="F58">
-        <v>-0.2064632670886593</v>
+        <v>-0.6084707960346623</v>
       </c>
       <c r="G58">
-        <v>-10.30518979549664</v>
+        <v>-10.86642658076928</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.805187196030337</v>
       </c>
       <c r="E59">
-        <v>-12.86083655917336</v>
+        <v>-16.02832751705248</v>
       </c>
       <c r="F59">
-        <v>-1.000349048379233</v>
+        <v>-0.7133396241268712</v>
       </c>
       <c r="G59">
-        <v>-11.03635357275453</v>
+        <v>-11.07594438685868</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.714033551875209</v>
       </c>
       <c r="E60">
-        <v>-14.1917686554497</v>
+        <v>-16.08397340565873</v>
       </c>
       <c r="F60">
-        <v>-0.6149469723897487</v>
+        <v>-0.6944263395861529</v>
       </c>
       <c r="G60">
-        <v>-10.97783305925684</v>
+        <v>-10.96370696144077</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.612631931529743</v>
       </c>
       <c r="E61">
-        <v>-15.31250710218602</v>
+        <v>-15.45279922694365</v>
       </c>
       <c r="F61">
-        <v>0.2059841762348257</v>
+        <v>-0.5645474428686212</v>
       </c>
       <c r="G61">
-        <v>-11.41966839856459</v>
+        <v>-11.53103183996013</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.5019720758772</v>
       </c>
       <c r="E62">
-        <v>-11.68678438794475</v>
+        <v>-15.8061198259701</v>
       </c>
       <c r="F62">
-        <v>-1.110190565990447</v>
+        <v>-0.5025598817497314</v>
       </c>
       <c r="G62">
-        <v>-12.68697171536191</v>
+        <v>-11.25016515640836</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.377965609434406</v>
       </c>
       <c r="E63">
-        <v>-14.38437371194394</v>
+        <v>-15.04138736334679</v>
       </c>
       <c r="F63">
-        <v>-1.696372333070475</v>
+        <v>-0.3417522313138746</v>
       </c>
       <c r="G63">
-        <v>-12.77803820205618</v>
+        <v>-11.42020470694195</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.237472630751828</v>
       </c>
       <c r="E64">
-        <v>-12.59569440602426</v>
+        <v>-14.4348888394995</v>
       </c>
       <c r="F64">
-        <v>-1.041140344395289</v>
+        <v>-0.8690395611570663</v>
       </c>
       <c r="G64">
-        <v>-11.11895499450489</v>
+        <v>-11.4379624732146</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.075989766478494</v>
       </c>
       <c r="E65">
-        <v>-12.63700314592223</v>
+        <v>-14.94783361882233</v>
       </c>
       <c r="F65">
-        <v>-0.2661471384603637</v>
+        <v>-0.9148896969020189</v>
       </c>
       <c r="G65">
-        <v>-10.57645589698452</v>
+        <v>-10.97104313035579</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.885434973451242</v>
       </c>
       <c r="E66">
-        <v>-10.29967657160326</v>
+        <v>-13.41375870703591</v>
       </c>
       <c r="F66">
-        <v>-0.8976066394100101</v>
+        <v>-0.6818185877155444</v>
       </c>
       <c r="G66">
-        <v>-10.36509411702975</v>
+        <v>-10.35176917123418</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.664093667011306</v>
       </c>
       <c r="E67">
-        <v>-11.95745580785721</v>
+        <v>-13.41317453388892</v>
       </c>
       <c r="F67">
-        <v>-1.517141791596357</v>
+        <v>-0.8583221436996463</v>
       </c>
       <c r="G67">
-        <v>-11.72883031484051</v>
+        <v>-10.66576448399744</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.408101398609195</v>
       </c>
       <c r="E68">
-        <v>-11.40044897643975</v>
+        <v>-14.31419595024707</v>
       </c>
       <c r="F68">
-        <v>-1.144168540118477</v>
+        <v>-0.7520575165337201</v>
       </c>
       <c r="G68">
-        <v>-11.99832196391934</v>
+        <v>-11.03853853281045</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.115052790228924</v>
       </c>
       <c r="E69">
-        <v>-11.05170666463505</v>
+        <v>-13.8952758767455</v>
       </c>
       <c r="F69">
-        <v>-0.6137002794485354</v>
+        <v>-0.6202294713174011</v>
       </c>
       <c r="G69">
-        <v>-12.19152871213674</v>
+        <v>-11.37504886578629</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.790256157802736</v>
       </c>
       <c r="E70">
-        <v>-11.80153139082511</v>
+        <v>-13.3233658373688</v>
       </c>
       <c r="F70">
-        <v>-0.5959425674347225</v>
+        <v>-0.8411310349893482</v>
       </c>
       <c r="G70">
-        <v>-12.74246307969118</v>
+        <v>-10.69656579969482</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.434378113182694</v>
       </c>
       <c r="E71">
-        <v>-12.20717850701019</v>
+        <v>-14.19549558955802</v>
       </c>
       <c r="F71">
-        <v>-0.9529564925302674</v>
+        <v>-1.004974651956465</v>
       </c>
       <c r="G71">
-        <v>-10.3220636461103</v>
+        <v>-10.59687534187074</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.053904176501852</v>
       </c>
       <c r="E72">
-        <v>-13.25329675904812</v>
+        <v>-14.16653146980496</v>
       </c>
       <c r="F72">
-        <v>-1.533225373089113</v>
+        <v>-1.034378381286236</v>
       </c>
       <c r="G72">
-        <v>-9.554944033750385</v>
+        <v>-11.40129818136717</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.6581122967880805</v>
       </c>
       <c r="E73">
-        <v>-11.82385676768292</v>
+        <v>-14.42648852021527</v>
       </c>
       <c r="F73">
-        <v>-1.385529950272169</v>
+        <v>-0.9847467483475041</v>
       </c>
       <c r="G73">
-        <v>-9.596289436990341</v>
+        <v>-10.50420655113546</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.2507565633843287</v>
       </c>
       <c r="E74">
-        <v>-11.50994747794522</v>
+        <v>-13.18918262404752</v>
       </c>
       <c r="F74">
-        <v>-1.117255711568924</v>
+        <v>-1.173848944160784</v>
       </c>
       <c r="G74">
-        <v>-9.528032609061649</v>
+        <v>-10.09037180599887</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.1566682492016621</v>
       </c>
       <c r="E75">
-        <v>-12.97278496511698</v>
+        <v>-14.44589303133814</v>
       </c>
       <c r="F75">
-        <v>-1.537081423349144</v>
+        <v>-0.6955048739445978</v>
       </c>
       <c r="G75">
-        <v>-10.55946286673144</v>
+        <v>-10.03949865269689</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.5571793316511446</v>
       </c>
       <c r="E76">
-        <v>-12.42868881309539</v>
+        <v>-14.20252378121792</v>
       </c>
       <c r="F76">
-        <v>-1.574333105453038</v>
+        <v>-0.6218423026506519</v>
       </c>
       <c r="G76">
-        <v>-8.346631327917333</v>
+        <v>-9.376621498277542</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.9463948277338337</v>
       </c>
       <c r="E77">
-        <v>-13.82839031565221</v>
+        <v>-14.49485489230907</v>
       </c>
       <c r="F77">
-        <v>-1.493549059597225</v>
+        <v>-1.331174138035271</v>
       </c>
       <c r="G77">
-        <v>-9.487531394934205</v>
+        <v>-9.449705101602492</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.314613510714913</v>
       </c>
       <c r="E78">
-        <v>-12.78092257836</v>
+        <v>-15.24976962328375</v>
       </c>
       <c r="F78">
-        <v>-1.439347323697248</v>
+        <v>-1.327805996175488</v>
       </c>
       <c r="G78">
-        <v>-9.186953723241617</v>
+        <v>-9.762727113977201</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.660058267157588</v>
       </c>
       <c r="E79">
-        <v>-12.84069843526125</v>
+        <v>-15.45239166428296</v>
       </c>
       <c r="F79">
-        <v>-1.103384699409046</v>
+        <v>-1.419033269878395</v>
       </c>
       <c r="G79">
-        <v>-9.265767880895046</v>
+        <v>-9.051184940130566</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.977222135460101</v>
       </c>
       <c r="E80">
-        <v>-13.80739178167864</v>
+        <v>-15.94224122616667</v>
       </c>
       <c r="F80">
-        <v>-1.941419149799222</v>
+        <v>-1.105322250764194</v>
       </c>
       <c r="G80">
-        <v>-8.606277414562372</v>
+        <v>-9.301028501433823</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.259399192903674</v>
       </c>
       <c r="E81">
-        <v>-15.24199876188659</v>
+        <v>-17.14787044665077</v>
       </c>
       <c r="F81">
-        <v>-2.140052540949113</v>
+        <v>-1.273611715582136</v>
       </c>
       <c r="G81">
-        <v>-8.136292506534199</v>
+        <v>-8.500273746394909</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.504004379491743</v>
       </c>
       <c r="E82">
-        <v>-13.97745862303671</v>
+        <v>-17.58042575538943</v>
       </c>
       <c r="F82">
-        <v>-1.144258832165382</v>
+        <v>-1.380992982007036</v>
       </c>
       <c r="G82">
-        <v>-7.564978420640013</v>
+        <v>-8.32093156289597</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.703749447502051</v>
       </c>
       <c r="E83">
-        <v>-17.49606934157455</v>
+        <v>-18.58693344528226</v>
       </c>
       <c r="F83">
-        <v>-1.278096496700893</v>
+        <v>-1.269551058573613</v>
       </c>
       <c r="G83">
-        <v>-6.15131257500597</v>
+        <v>-7.57321174739618</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.853507609874691</v>
       </c>
       <c r="E84">
-        <v>-17.54965930298132</v>
+        <v>-18.91268469455002</v>
       </c>
       <c r="F84">
-        <v>-1.710339435849078</v>
+        <v>-1.406031215124054</v>
       </c>
       <c r="G84">
-        <v>-7.128380364375389</v>
+        <v>-8.123957413854875</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.949128670747283</v>
       </c>
       <c r="E85">
-        <v>-18.45382800877481</v>
+        <v>-20.03790633055393</v>
       </c>
       <c r="F85">
-        <v>-2.137996533055365</v>
+        <v>-1.940562617904728</v>
       </c>
       <c r="G85">
-        <v>-7.392409613314423</v>
+        <v>-7.232798281229542</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.985722596322768</v>
       </c>
       <c r="E86">
-        <v>-17.75511616870932</v>
+        <v>-20.35873060010134</v>
       </c>
       <c r="F86">
-        <v>-1.337586530100342</v>
+        <v>-1.84867513538179</v>
       </c>
       <c r="G86">
-        <v>-7.134137403068181</v>
+        <v>-7.469638019654542</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.961423359193802</v>
       </c>
       <c r="E87">
-        <v>-20.47004501968389</v>
+        <v>-21.82645431072738</v>
       </c>
       <c r="F87">
-        <v>-1.850049396903034</v>
+        <v>-1.947639360626844</v>
       </c>
       <c r="G87">
-        <v>-6.26691682523732</v>
+        <v>-7.024343160258253</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.876110960271363</v>
       </c>
       <c r="E88">
-        <v>-21.44043812936555</v>
+        <v>-23.27702416181237</v>
       </c>
       <c r="F88">
-        <v>-2.494602073021329</v>
+        <v>-1.766455528816925</v>
       </c>
       <c r="G88">
-        <v>-5.902392655908169</v>
+        <v>-6.304825882207513</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.732223642616044</v>
       </c>
       <c r="E89">
-        <v>-22.91039437767737</v>
+        <v>-24.59234660818427</v>
       </c>
       <c r="F89">
-        <v>-2.260331487835601</v>
+        <v>-2.158826659766161</v>
       </c>
       <c r="G89">
-        <v>-5.408409603265818</v>
+        <v>-6.574469816381152</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.53298169782174</v>
       </c>
       <c r="E90">
-        <v>-25.40889387040334</v>
+        <v>-24.78804914089975</v>
       </c>
       <c r="F90">
-        <v>-2.449219964858958</v>
+        <v>-2.501652307986556</v>
       </c>
       <c r="G90">
-        <v>-6.586586413054884</v>
+        <v>-7.283704539986915</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.286705702161888</v>
       </c>
       <c r="E91">
-        <v>-26.35194405402668</v>
+        <v>-27.32675242586582</v>
       </c>
       <c r="F91">
-        <v>-3.463459758968228</v>
+        <v>-2.361239063007623</v>
       </c>
       <c r="G91">
-        <v>-4.47907657002715</v>
+        <v>-6.812339134468865</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.000908003160006</v>
       </c>
       <c r="E92">
-        <v>-29.11627402795093</v>
+        <v>-28.75138770630888</v>
       </c>
       <c r="F92">
-        <v>-3.098401558024098</v>
+        <v>-2.549847551848834</v>
       </c>
       <c r="G92">
-        <v>-5.714194763091681</v>
+        <v>-6.786467221079461</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.683478507398165</v>
       </c>
       <c r="E93">
-        <v>-28.27390087846611</v>
+        <v>-29.48313023578631</v>
       </c>
       <c r="F93">
-        <v>-3.300785796773864</v>
+        <v>-2.632976705821973</v>
       </c>
       <c r="G93">
-        <v>-6.873253172391455</v>
+        <v>-6.417000407260178</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.345869281456913</v>
       </c>
       <c r="E94">
-        <v>-30.32461127589161</v>
+        <v>-31.72332783535177</v>
       </c>
       <c r="F94">
-        <v>-3.854126109802503</v>
+        <v>-2.95628850313462</v>
       </c>
       <c r="G94">
-        <v>-6.458643759598671</v>
+        <v>-6.850102527435332</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.9947299253199285</v>
       </c>
       <c r="E95">
-        <v>-32.59622969235929</v>
+        <v>-33.14424750287153</v>
       </c>
       <c r="F95">
-        <v>-4.10379770174108</v>
+        <v>-3.323000953782141</v>
       </c>
       <c r="G95">
-        <v>-5.766471587702312</v>
+        <v>-7.853710960393088</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.6363719058291215</v>
       </c>
       <c r="E96">
-        <v>-35.99298143958774</v>
+        <v>-35.34931093684848</v>
       </c>
       <c r="F96">
-        <v>-3.640016330466109</v>
+        <v>-3.478996617975136</v>
       </c>
       <c r="G96">
-        <v>-7.390261069259436</v>
+        <v>-7.134044707793082</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.2814553084259958</v>
       </c>
       <c r="E97">
-        <v>-35.89710685213434</v>
+        <v>-38.05632627949464</v>
       </c>
       <c r="F97">
-        <v>-4.946255634062205</v>
+        <v>-3.895159289100177</v>
       </c>
       <c r="G97">
-        <v>-6.684446139195741</v>
+        <v>-7.581491421789897</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.0759212664051984</v>
       </c>
       <c r="E98">
-        <v>-38.40140505582714</v>
+        <v>-40.42472271398024</v>
       </c>
       <c r="F98">
-        <v>-4.430201794568378</v>
+        <v>-4.011114986511454</v>
       </c>
       <c r="G98">
-        <v>-7.526096063281273</v>
+        <v>-8.327486443063727</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.4194719876370164</v>
       </c>
       <c r="E99">
-        <v>-40.62853347940646</v>
+        <v>-41.03502742023098</v>
       </c>
       <c r="F99">
-        <v>-5.331428252281113</v>
+        <v>-4.470575593413423</v>
       </c>
       <c r="G99">
-        <v>-6.870568319959106</v>
+        <v>-7.131032111352345</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.7669151464477533</v>
       </c>
       <c r="E100">
-        <v>-43.28484576282574</v>
+        <v>-44.27961111961668</v>
       </c>
       <c r="F100">
-        <v>-5.679233216959736</v>
+        <v>-4.650772011279204</v>
       </c>
       <c r="G100">
-        <v>-6.941473584319216</v>
+        <v>-7.681969789452317</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.092060845682189</v>
       </c>
       <c r="E101">
-        <v>-43.95078277226071</v>
+        <v>-45.62088172205253</v>
       </c>
       <c r="F101">
-        <v>-6.026464951395622</v>
+        <v>-5.191768821638728</v>
       </c>
       <c r="G101">
-        <v>-6.034261616373958</v>
+        <v>-7.986410867789234</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.440405427127147</v>
       </c>
       <c r="E102">
-        <v>-48.28483354112275</v>
+        <v>-49.206570461829</v>
       </c>
       <c r="F102">
-        <v>-5.725717053767831</v>
+        <v>-5.272378910339953</v>
       </c>
       <c r="G102">
-        <v>-8.292315207254511</v>
+        <v>-8.266886906967368</v>
       </c>
     </row>
   </sheetData>
